--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486347_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486347_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1991</v>
+        <v>7.2296</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7449</v>
+        <v>4.4226</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4542</v>
+        <v>2.807</v>
       </c>
       <c r="G2" t="n">
         <v>7.9521</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1407</v>
+        <v>-0.1103</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1524</v>
+        <v>-0.4747</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0117</v>
+        <v>0.3644</v>
       </c>
       <c r="V2" t="n">
         <v>2.6504</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7126</v>
+        <v>5.3111</v>
       </c>
       <c r="E3" t="n">
-        <v>4.476</v>
+        <v>4.8119</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2366</v>
+        <v>0.4991</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7004</v>
+        <v>6.34</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0814</v>
+        <v>2.6641</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.381</v>
+        <v>3.6759</v>
       </c>
       <c r="J3" t="n">
-        <v>3.562</v>
+        <v>7.3307</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7771</v>
+        <v>1.9558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7849</v>
+        <v>5.3748</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8616</v>
+        <v>-0.9907</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3043</v>
+        <v>0.7083</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1659</v>
+        <v>-1.6989</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9576</v>
+        <v>-0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R3" t="n">
-        <v>3.0451</v>
+        <v>2.1751</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4897</v>
+        <v>-1.029</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2584</v>
+        <v>-0.3437</v>
       </c>
       <c r="U3" t="n">
-        <v>0.748</v>
+        <v>-0.6853</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9767</v>
+        <v>5.1457</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6317</v>
+        <v>4.3715</v>
       </c>
       <c r="F4" t="n">
-        <v>0.345</v>
+        <v>0.7742</v>
       </c>
       <c r="G4" t="n">
-        <v>6.34</v>
+        <v>2.7004</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6641</v>
+        <v>4.0814</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6759</v>
+        <v>-1.381</v>
       </c>
       <c r="J4" t="n">
-        <v>7.3307</v>
+        <v>3.562</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9558</v>
+        <v>2.7771</v>
       </c>
       <c r="L4" t="n">
-        <v>5.3748</v>
+        <v>0.7849</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9907</v>
+        <v>-0.8616</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7083</v>
+        <v>1.3043</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6989</v>
+        <v>-2.1659</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>1.9576</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1751</v>
+        <v>3.0451</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3633</v>
+        <v>-0.0772</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5239</v>
+        <v>-0.3629</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8394</v>
+        <v>0.2857</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2889</v>
+        <v>3.0996</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8448</v>
+        <v>0.9638</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4441</v>
+        <v>2.1358</v>
       </c>
       <c r="G5" t="n">
         <v>-1.221</v>
@@ -844,13 +844,13 @@
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.4957</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3953</v>
+        <v>-0.2764</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0803</v>
+        <v>0.7721</v>
       </c>
       <c r="V5" t="n">
         <v>3.3899</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4805</v>
+        <v>1.9084</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6287</v>
+        <v>1.6939</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8518</v>
+        <v>0.2145</v>
       </c>
       <c r="G6" t="n">
-        <v>1.321</v>
+        <v>0.6181</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4835</v>
+        <v>1.168</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8375</v>
+        <v>-0.5498</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2725</v>
+        <v>1.5219</v>
       </c>
       <c r="K6" t="n">
-        <v>0.584</v>
+        <v>1.1378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6885</v>
+        <v>0.3841</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0486</v>
+        <v>-0.9038</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1004</v>
+        <v>0.0302</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-0.9339</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1233</v>
+        <v>-0.6021</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.274</v>
+        <v>-0.3929</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1507</v>
+        <v>-0.2091</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3698</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3698</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1095</v>
+        <v>1.8525</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2649</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1554</v>
+        <v>0.9751</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6181</v>
+        <v>1.321</v>
       </c>
       <c r="H7" t="n">
-        <v>1.168</v>
+        <v>0.4835</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5498</v>
+        <v>0.8375</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5219</v>
+        <v>1.2725</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1378</v>
+        <v>0.584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3841</v>
+        <v>0.6885</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9038</v>
+        <v>0.0486</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0302</v>
+        <v>-0.1004</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9339</v>
+        <v>0.149</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4009</v>
+        <v>0.2488</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.0252</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.579</v>
+        <v>0.274</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3698</v>
+        <v>-0.3698</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5649999999999999</v>
+        <v>-0.3698</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1359</v>
+        <v>0.6449</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0538</v>
+        <v>0.4396</v>
       </c>
       <c r="F8" t="n">
-        <v>0.082</v>
+        <v>0.2053</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3763</v>
@@ -1078,13 +1078,13 @@
         <v>2.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0979</v>
+        <v>-0.5888</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0274</v>
+        <v>-0.6417</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0704</v>
+        <v>0.0529</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5649999999999999</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1353</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4396</v>
+        <v>0.1728</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5748</v>
+        <v>-0.2666</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0788</v>
@@ -1156,13 +1156,13 @@
         <v>0.2175</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.274</v>
+        <v>-0.2325</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1971</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4711</v>
+        <v>-0.1628</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5764</v>
+        <v>-0.4463</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9505</v>
+        <v>-0.882</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3741</v>
+        <v>0.4358</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6294999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1644</v>
+        <v>-0.0342</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2055</v>
+        <v>-0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0411</v>
+        <v>0.1027</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7036</v>
+        <v>-1.3129</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5908</v>
+        <v>-0.5422</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1128</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0613</v>
+        <v>-0.7193000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3345</v>
+        <v>1.9765</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7267</v>
+        <v>-2.6958</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3783</v>
+        <v>-0.1198</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4166</v>
+        <v>0.6236</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0382</v>
+        <v>-0.7433999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6829</v>
+        <v>-0.5995</v>
       </c>
       <c r="N11" t="n">
-        <v>0.082</v>
+        <v>1.3529</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.765</v>
+        <v>-1.9523</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6525</v>
+        <v>2.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.435</v>
+        <v>2.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1644</v>
+        <v>-1.2483</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.125</v>
+        <v>-0.6177</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0394</v>
+        <v>-0.6306</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1745</v>
+        <v>-1.5204</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1745</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8459</v>
+        <v>-1.642</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8595</v>
+        <v>-1.5908</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9864000000000001</v>
+        <v>-0.0512</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7193000000000001</v>
+        <v>-1.0613</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9765</v>
+        <v>-0.3345</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6958</v>
+        <v>-0.7267</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.1198</v>
+        <v>-0.3783</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6236</v>
+        <v>-0.4166</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.7433999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5995</v>
+        <v>-0.6829</v>
       </c>
       <c r="N12" t="n">
-        <v>1.3529</v>
+        <v>0.082</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9523</v>
+        <v>-0.765</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1751</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>2.1751</v>
+        <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7813</v>
+        <v>-0.1027</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9349</v>
+        <v>-0.125</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8464</v>
+        <v>0.0222</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5204</v>
+        <v>0.1745</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7156</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.642</v>
+        <v>21.6968</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6836</v>
+        <v>14.7386</v>
       </c>
       <c r="F13" t="n">
-        <v>6.958400000000001</v>
+        <v>6.958300000000001</v>
       </c>
       <c r="G13" t="n">
         <v>14.8454</v>
@@ -1438,19 +1438,19 @@
         <v>12.0884</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7572</v>
+        <v>2.757200000000001</v>
       </c>
       <c r="J13" t="n">
         <v>20.7598</v>
       </c>
       <c r="K13" t="n">
-        <v>7.0734</v>
+        <v>7.073399999999999</v>
       </c>
       <c r="L13" t="n">
         <v>13.6862</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.914300000000001</v>
+        <v>-5.9143</v>
       </c>
       <c r="N13" t="n">
         <v>5.0149</v>
@@ -1468,13 +1468,13 @@
         <v>16.313</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.335500000000001</v>
+        <v>-3.2806</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.5217</v>
+        <v>-3.4669</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1860999999999997</v>
+        <v>0.1862000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>4.6944</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>S. RODRÍGUEZ RAMOS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5048</v>
+        <v>0.1586</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4883</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9835</v>
+        <v>0.2335</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.5519</v>
+        <v>-0.6148</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3685</v>
+        <v>-2.2475</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.1834</v>
+        <v>1.6328</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5492</v>
+        <v>1.301</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7022</v>
+        <v>-1.7972</v>
       </c>
       <c r="L14" t="n">
-        <v>0.153</v>
+        <v>3.0982</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.0027</v>
+        <v>-1.9158</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6663</v>
+        <v>-0.4504</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.3364</v>
+        <v>-1.4654</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9679</v>
+        <v>0.5336</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5622</v>
+        <v>-0.2884</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4057</v>
+        <v>0.822</v>
       </c>
       <c r="V14" t="n">
-        <v>2.6113</v>
+        <v>-0.1952</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6504</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.039</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. RODRÍGUEZ RAMOS</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4144</v>
+        <v>-0.4381</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.3707</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3311</v>
+        <v>-0.8088</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6148</v>
+        <v>-2.5519</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.2475</v>
+        <v>-1.3685</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6328</v>
+        <v>-1.1834</v>
       </c>
       <c r="J15" t="n">
-        <v>1.301</v>
+        <v>-0.5492</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7972</v>
+        <v>-0.7022</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0982</v>
+        <v>0.153</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9158</v>
+        <v>-2.0027</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4504</v>
+        <v>-0.6663</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4654</v>
+        <v>-1.3364</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0394</v>
+        <v>1.025</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>0.4446</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9195</v>
+        <v>0.5804</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>2.6113</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.6504</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9141</v>
+        <v>-0.5848</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.375</v>
+        <v>1.465</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5391</v>
+        <v>-2.0497</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2369</v>
+        <v>-0.3659</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.742</v>
+        <v>-0.891</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4949</v>
+        <v>0.5251</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4646</v>
+        <v>1.6368</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5411</v>
+        <v>-0.3737</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0765</v>
+        <v>2.0105</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7723</v>
+        <v>-2.0027</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2009</v>
+        <v>-0.5173</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5714</v>
+        <v>-1.4854</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.5225</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8839</v>
+        <v>0.5576</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8292</v>
+        <v>-0.1718</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0547</v>
+        <v>0.7294</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7786</v>
+        <v>-2.299</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.039</v>
+        <v>-2.299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2039</v>
+        <v>-1.0404</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2414</v>
+        <v>-1.5995</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4453</v>
+        <v>0.5591</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3659</v>
+        <v>2.1526</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.891</v>
+        <v>2.0498</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5251</v>
+        <v>0.1028</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6368</v>
+        <v>3.5233</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3737</v>
+        <v>2.3177</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0105</v>
+        <v>1.2057</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0027</v>
+        <v>-1.3707</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5173</v>
+        <v>-0.2679</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4854</v>
+        <v>-1.1029</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5225</v>
+        <v>-4.7852</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-5.4377</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0615</v>
+        <v>1.2224</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3953</v>
+        <v>0.3149</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3338</v>
+        <v>0.9076</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.299</v>
+        <v>0.3698</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.299</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2934</v>
+        <v>-1.3933</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4877</v>
+        <v>-1.1573</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1944</v>
+        <v>-0.236</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1526</v>
+        <v>-1.2369</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0498</v>
+        <v>-0.742</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1028</v>
+        <v>-0.4949</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5233</v>
+        <v>-0.4646</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3177</v>
+        <v>-0.5411</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2057</v>
+        <v>0.0765</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3707</v>
+        <v>-0.7723</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2679</v>
+        <v>-0.2009</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1029</v>
+        <v>-0.5714</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.7852</v>
+        <v>0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.4377</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9694</v>
+        <v>0.4047</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4266</v>
+        <v>0.0469</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.3578</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3698</v>
+        <v>-0.7786</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3698</v>
+        <v>-0.039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. KANDE KIELI</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7125</v>
+        <v>-1.442</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5962</v>
+        <v>-0.1785</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3087</v>
+        <v>-1.2636</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4175</v>
+        <v>-0.7692</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2461</v>
+        <v>-2.2872</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1714</v>
+        <v>1.518</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9142</v>
+        <v>1.714</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6847</v>
+        <v>-1.2894</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2295</v>
+        <v>3.0034</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.3318</v>
+        <v>-2.4832</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.9978</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.4009</v>
+        <v>-1.4854</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3772</v>
+        <v>0.7622</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4867</v>
+        <v>-0.2824</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8904</v>
+        <v>1.0446</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.1947</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3899</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>G. KANDE KIELI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9815</v>
+        <v>-2.1596</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6254999999999999</v>
+        <v>1.1491</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.356</v>
+        <v>-3.3087</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7692</v>
+        <v>-1.4175</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.2872</v>
+        <v>-0.2461</v>
       </c>
       <c r="I20" t="n">
-        <v>1.518</v>
+        <v>-1.1714</v>
       </c>
       <c r="J20" t="n">
-        <v>1.714</v>
+        <v>0.9142</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2894</v>
+        <v>0.6847</v>
       </c>
       <c r="L20" t="n">
-        <v>3.0034</v>
+        <v>0.2295</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.4832</v>
+        <v>-2.3318</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9978</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4854</v>
+        <v>-1.4009</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.87</v>
+        <v>1.5225</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.305</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2227</v>
+        <v>0.9301</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7294</v>
+        <v>0.0397</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.8904</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-3.1947</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.13</v>
+        <v>-3.3899</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5545</v>
+        <v>-2.654</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3354</v>
+        <v>-1.5531</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2191</v>
+        <v>-1.1009</v>
       </c>
       <c r="G21" t="n">
         <v>-3.7587</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.084</v>
+        <v>-0.1836</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3579</v>
+        <v>-0.5756</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2739</v>
+        <v>0.392</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2343</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2723</v>
+        <v>-3.3268</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.7888</v>
+        <v>-2.8948</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4835</v>
+        <v>-0.432</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3156</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2004</v>
+        <v>0.7451</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.0277</v>
       </c>
       <c r="U22" t="n">
-        <v>0.666</v>
+        <v>0.7174</v>
       </c>
       <c r="V22" t="n">
         <v>0.1562</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8002</v>
+        <v>-5.2716</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9263</v>
+        <v>-2.4851</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8739</v>
+        <v>-2.7865</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9676</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>1.3</v>
+        <v>0.8286</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8172</v>
+        <v>0.2584</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4828</v>
+        <v>0.5702</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-19.642</v>
+        <v>-18.152</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.958299999999999</v>
+        <v>-6.9584</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.6836</v>
+        <v>-11.1936</v>
       </c>
       <c r="G24" t="n">
         <v>-14.8455</v>
@@ -2299,7 +2299,7 @@
         <v>-2.757199999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>5.914299999999999</v>
+        <v>5.914300000000001</v>
       </c>
       <c r="K24" t="n">
         <v>-5.0147</v>
@@ -2326,19 +2326,19 @@
         <v>10.875</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3358</v>
+        <v>6.825699999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1859999999999996</v>
+        <v>-0.1860000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>5.5217</v>
+        <v>7.011799999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-4.6945</v>
       </c>
       <c r="W24" t="n">
-        <v>3.6266</v>
+        <v>3.626599999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-8.3209</v>
